--- a/assets/constructions/examples/ctd_tko_radial_groove.xlsx
+++ b/assets/constructions/examples/ctd_tko_radial_groove.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,11 +619,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VE11005GS W200T230 LVTX</t>
+          <t>VE11005GS W142T230 LVTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -659,7 +684,7 @@
         <v>5.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -731,11 +756,30 @@
           <t>2021/Groovex Vargus</t>
         </is>
       </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>2209.17</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V11GSW250T230RVTX</t>
+          <t>V11GSW150T230R VBX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -779,7 +823,7 @@
         <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
         <v>-0.03</v>
@@ -821,12 +865,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -849,13 +893,24 @@
       <c r="AL3" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V11GSRW200T230R VBX</t>
+          <t>V16GSRW117T430RVTX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -870,7 +925,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>V11</t>
+          <t>V16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -885,21 +940,21 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
         <v>11</v>
       </c>
-      <c r="I4" t="n">
-        <v>8</v>
-      </c>
       <c r="J4" t="n">
-        <v>6.7</v>
+        <v>10.2</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="O4" t="n">
         <v>-0.03</v>
@@ -908,7 +963,7 @@
         <v>0.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="R4" t="n">
         <v>0.2</v>
@@ -931,7 +986,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>VARGUS_V11</t>
+          <t>VARGUS_V16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -941,12 +996,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -969,13 +1024,32 @@
       <c r="AL4" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>2367.29</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VE11005GS W238T230 LVTX</t>
+          <t>V08D472W110T100R VBX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -988,8 +1062,16 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -997,33 +1079,33 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.38</v>
+        <v>1.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="P5" t="n">
         <v>0.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1031,7 +1113,7 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1043,7 +1125,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>VARGUS_V11</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1053,12 +1135,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -1080,14 +1162,25 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VE08020GSW150T100L VTX</t>
+          <t>V11GSRW157T230RVTX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1100,8 +1193,16 @@
           <t>Mini-V</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -1109,30 +1210,30 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="P6" t="n">
         <v>0.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
         <v>0.2</v>
@@ -1143,7 +1244,7 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1155,7 +1256,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>VARGUS_V11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1192,7 +1293,18 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
